--- a/docs/downloads/经营分_鲁西省区__德州片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_鲁西省区__德州片区_2026-10-18.xlsx
@@ -885,7 +885,7 @@
         <v>86</v>
       </c>
       <c r="I4" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1387,33 +1387,33 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>7235879668824410112</t>
+          <t>6601141489189783556</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>希岸酒店（德州齐河经济开发区欧乐堡万达店）</t>
+          <t>维也纳国际酒店（德州扒鸡美食城店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>希岸酒店(德州齐河经济开发区欧乐堡万达店)</t>
+          <t>维也纳国际酒店(德州扒鸡美食城店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H10" t="n">
         <v>95</v>
       </c>
       <c r="I10" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1423,19 +1423,19 @@
         <v>10</v>
       </c>
       <c r="M10" t="n">
+        <v>30</v>
+      </c>
+      <c r="N10" t="n">
+        <v>30</v>
+      </c>
+      <c r="O10" t="n">
+        <v>20</v>
+      </c>
+      <c r="P10" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q10" t="n">
         <v>15</v>
-      </c>
-      <c r="N10" t="n">
-        <v>30</v>
-      </c>
-      <c r="O10" t="n">
-        <v>25</v>
-      </c>
-      <c r="P10" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>25</v>
       </c>
       <c r="R10" t="n">
         <v>30</v>
@@ -1475,37 +1475,37 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>6601141489189783556</t>
+          <t>7007632116246661151</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（德州扒鸡美食城店）</t>
+          <t>麗枫酒店（德州齐河经济开发区欧乐堡店）</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(德州扒鸡美食城店)</t>
+          <t>麗枫酒店(德州齐河经济开发区店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>搭门店,提质量,拿收益</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
         <v>30</v>
       </c>
       <c r="Q11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R11" t="n">
         <v>30</v>
@@ -1563,17 +1563,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>7007632116246661151</t>
+          <t>7426232997705156619</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>麗枫酒店（德州齐河经济开发区欧乐堡店）</t>
+          <t>7天酒店（宁津客运中心店）</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>麗枫酒店(德州齐河经济开发区店)</t>
+          <t>7天酒店(宁津客运中心店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1582,24 +1582,24 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>搭门店,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L12" t="n">
         <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N12" t="n">
         <v>30</v>
@@ -1611,7 +1611,7 @@
         <v>30</v>
       </c>
       <c r="Q12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R12" t="n">
         <v>30</v>
@@ -1651,33 +1651,33 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>6668065845706573838</t>
+          <t>7235879668824410112</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7天优品（德州学院南门店）</t>
+          <t>希岸酒店（德州齐河经济开发区欧乐堡万达店）</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>7天优品(德州学院南门店)</t>
+          <t>希岸酒店(德州齐河经济开发区欧乐堡万达店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>100</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1687,19 +1687,19 @@
         <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N13" t="n">
         <v>30</v>
       </c>
       <c r="O13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P13" t="n">
         <v>30</v>
       </c>
       <c r="Q13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R13" t="n">
         <v>30</v>
@@ -1739,17 +1739,17 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>7426232997705156619</t>
+          <t>7639528301635864610</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7天酒店（宁津客运中心店）</t>
+          <t>白玉兰酒店（德州齐河欧乐堡黄河水街店）</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7天酒店(宁津客运中心店)</t>
+          <t>白玉兰酒店(德州齐河欧乐堡黄河水街店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1761,7 +1761,7 @@
         <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>7639528301635864610</t>
+          <t>7125309216293980191</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>白玉兰酒店（德州齐河欧乐堡黄河水街店）</t>
+          <t>维也纳酒店（5.0德州平原德百金街店）</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>白玉兰酒店(德州齐河欧乐堡黄河水街店)</t>
+          <t>维也纳酒店(5.0山东德州平原德百金街店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1849,11 +1849,11 @@
         <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1863,7 +1863,7 @@
         <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N15" t="n">
         <v>30</v>
@@ -1875,7 +1875,7 @@
         <v>30</v>
       </c>
       <c r="Q15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R15" t="n">
         <v>30</v>
@@ -1915,17 +1915,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>7125309216293980191</t>
+          <t>6601133363405260803</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0德州平原德百金街店）</t>
+          <t>维也纳酒店（德州万达广场店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0山东德州平原德百金街店)</t>
+          <t>维也纳酒店(德州万达广场店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1951,13 +1951,13 @@
         <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N16" t="n">
         <v>30</v>
       </c>
       <c r="O16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P16" t="n">
         <v>30</v>
@@ -2003,17 +2003,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>6601133363405260803</t>
+          <t>7463654702341687315</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>维也纳酒店（德州万达广场店）</t>
+          <t>麗枫酒店（德州平原共青团路店）</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>维也纳酒店(德州万达广场店)</t>
+          <t>麗枫酒店(德州平原共青团路店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2025,11 +2025,11 @@
         <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2039,13 +2039,13 @@
         <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N17" t="n">
         <v>30</v>
       </c>
       <c r="O17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P17" t="n">
         <v>30</v>
@@ -2091,17 +2091,17 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7463654702341687315</t>
+          <t>6668065845706573838</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>麗枫酒店（德州平原共青团路店）</t>
+          <t>7天优品（德州学院南门店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>麗枫酒店(德州平原共青团路店)</t>
+          <t>7天优品(德州学院南门店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>30</v>
       </c>
       <c r="Q18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R18" t="n">
         <v>30</v>
@@ -2993,7 +2993,7 @@
         <v>110</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -3059,29 +3059,29 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>7306421629198338099</t>
+          <t>7002802900720977950</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>凯里亚德酒店（3.0版德州学院店）</t>
+          <t>白玉兰（商务）酒店德州新湖风景区解放南大道店</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>凯里亚德酒店(德州学院店)</t>
+          <t>白玉兰(商务)酒店(德州新湖风景区解放南大道店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>110</v>
       </c>
       <c r="I29" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -3147,26 +3147,26 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>7002802900720977950</t>
+          <t>7306421629198338099</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>白玉兰（商务）酒店德州新湖风景区解放南大道店</t>
+          <t>凯里亚德酒店（3.0版德州学院店）</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>白玉兰(商务)酒店(德州新湖风景区解放南大道店)</t>
+          <t>凯里亚德酒店(德州学院店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -3195,7 +3195,7 @@
         <v>30</v>
       </c>
       <c r="Q30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R30" t="n">
         <v>30</v>
@@ -3235,17 +3235,17 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>7247093568383223860</t>
+          <t>7309349339376125991</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（山东德州陵城店）</t>
+          <t>白玉兰商务酒店（德州武城县广场店）</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(山东德州陵城店)</t>
+          <t>白玉兰商务酒店(武城县广场店)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>30</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R31" t="n">
         <v>30</v>
@@ -3323,17 +3323,17 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>7309349339376125991</t>
+          <t>7247093568383223860</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（德州武城县广场店）</t>
+          <t>维也纳3好酒店（山东德州陵城店）</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店(武城县广场店)</t>
+          <t>维也纳3好酒店(山东德州陵城店)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3345,7 +3345,7 @@
         <v>115</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>115</v>
       </c>
       <c r="I34" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>115</v>
       </c>
       <c r="I35" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
